--- a/Benchmarking_USA.xlsx
+++ b/Benchmarking_USA.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8556" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8556"/>
   </bookViews>
   <sheets>
-    <sheet name="benchmarking_cs" sheetId="1" r:id="rId1"/>
-    <sheet name="benchmarking_ds" sheetId="2" r:id="rId2"/>
-    <sheet name="benchmarking_business" sheetId="3" r:id="rId3"/>
-    <sheet name="benchmarking_finance&amp;economic" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="benchmarking_cs" sheetId="1" r:id="rId2"/>
+    <sheet name="benchmarking_ds" sheetId="2" r:id="rId3"/>
+    <sheet name="benchmarking_business" sheetId="3" r:id="rId4"/>
+    <sheet name="benchmarking_finance&amp;economic" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="254">
   <si>
     <t>Global Rank</t>
   </si>
@@ -711,13 +712,91 @@
   </si>
   <si>
     <t>WU Vienna University of Economics and Business</t>
+  </si>
+  <si>
+    <t>course</t>
+  </si>
+  <si>
+    <t>benchmarking_set</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>benchmarking_cs</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>benchmarking_ds</t>
+  </si>
+  <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>benchmarking_bio</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>benchmarking_chem</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>benchmarking_math</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>benchmarking_phys</t>
+  </si>
+  <si>
+    <t>Environmental Science</t>
+  </si>
+  <si>
+    <t>benchmarking_envsci</t>
+  </si>
+  <si>
+    <t>Biomedical Engineering</t>
+  </si>
+  <si>
+    <t>benchmarking_bme</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>benchmarking_stats</t>
+  </si>
+  <si>
+    <t>Robotics and Automation</t>
+  </si>
+  <si>
+    <t>benchmarking_robotics</t>
+  </si>
+  <si>
+    <t>Business and Administration</t>
+  </si>
+  <si>
+    <t>benchmarking_business</t>
+  </si>
+  <si>
+    <t>Finance and Economics</t>
+  </si>
+  <si>
+    <t>benchmarking_finance&amp;eco.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,6 +820,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -759,10 +860,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -779,9 +881,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1059,6 +1166,120 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5416,7 +5637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6349,7 +6570,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -6393,7 +6614,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -6437,7 +6658,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -6481,7 +6702,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -8774,7 +8995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N95"/>
   <sheetFormatPr defaultColWidth="28.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12946,7 +13167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
